--- a/data/raw/evds.xlsx
+++ b/data/raw/evds.xlsx
@@ -70608,105 +70608,175 @@
       </c>
     </row>
     <row r="2032">
-</row>
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>14-10-2026</t>
+        </is>
+      </c>
+      <c r="B2032" s="2" t="n">
+        <v>36.7693</v>
+      </c>
+      <c r="C2032" s="2" t="n">
+        <v>49.2794</v>
+      </c>
+      <c r="D2032" s="2" t="n">
+        <v>49.3681</v>
+      </c>
+      <c r="E2032" s="2" t="n">
+        <v>55.1128</v>
+      </c>
+      <c r="F2032" s="2" t="n">
+        <v>55.2121</v>
+      </c>
+      <c r="G2032" s="2" t="n">
+        <v>65.1201</v>
+      </c>
+      <c r="H2032" s="2" t="n">
+        <v>65.4596</v>
+      </c>
+      <c r="I2032" s="2" t="n">
+        <v>31.0945</v>
+      </c>
+      <c r="J2032" s="2" t="n">
+        <v>31.3004</v>
+      </c>
+    </row>
     <row r="2033">
-</row>
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>15-10-2026</t>
+        </is>
+      </c>
+      <c r="B2033" s="2" t="n">
+        <v>36.7892</v>
+      </c>
+      <c r="C2033" s="2" t="n">
+        <v>49.3041</v>
+      </c>
+      <c r="D2033" s="2" t="n">
+        <v>49.3929</v>
+      </c>
+      <c r="E2033" s="2" t="n">
+        <v>55.2033</v>
+      </c>
+      <c r="F2033" s="2" t="n">
+        <v>55.3027</v>
+      </c>
+      <c r="G2033" s="2" t="n">
+        <v>65.291</v>
+      </c>
+      <c r="H2033" s="2" t="n">
+        <v>65.6314</v>
+      </c>
+      <c r="I2033" s="2" t="n">
+        <v>31.0528</v>
+      </c>
+      <c r="J2033" s="2" t="n">
+        <v>31.2585</v>
+      </c>
+    </row>
     <row r="2034">
-      <c r="A2034" s="1" t="inlineStr">
-        <is>
-          <t>Seri Açıklamaları</t>
-        </is>
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>16-10-2026</t>
+        </is>
+      </c>
+      <c r="B2034" s="2" t="n">
+        <v>36.7953</v>
+      </c>
+      <c r="C2034" s="2" t="n">
+        <v>49.3315</v>
+      </c>
+      <c r="D2034" s="2" t="n">
+        <v>49.4204</v>
+      </c>
+      <c r="E2034" s="2" t="n">
+        <v>55.3113</v>
+      </c>
+      <c r="F2034" s="2" t="n">
+        <v>55.411</v>
+      </c>
+      <c r="G2034" s="2" t="n">
+        <v>65.2551</v>
+      </c>
+      <c r="H2034" s="2" t="n">
+        <v>65.5953</v>
+      </c>
+      <c r="I2034" s="2" t="n">
+        <v>31.1777</v>
+      </c>
+      <c r="J2034" s="2" t="n">
+        <v>31.3842</v>
       </c>
     </row>
     <row r="2035">
       <c r="A2035" t="inlineStr">
         <is>
-          <t>TP.BISTTLREF.ORAN</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="B2035" t="inlineStr">
         <is>
-          <t>BIST TLREF -Türk Lirası Gecelik Referans Faiz Oranı (ISIN:TRIXIST00015)-Düzey</t>
-        </is>
+          <t/>
+        </is>
+      </c>
+      <c r="C2035" s="2" t="n">
+        <v>49.3573</v>
+      </c>
+      <c r="D2035" s="2" t="n">
+        <v>49.4463</v>
+      </c>
+      <c r="E2035" s="2" t="n">
+        <v>55.5179</v>
+      </c>
+      <c r="F2035" s="2" t="n">
+        <v>55.618</v>
+      </c>
+      <c r="G2035" s="2" t="n">
+        <v>65.6633</v>
+      </c>
+      <c r="H2035" s="2" t="n">
+        <v>66.0056</v>
+      </c>
+      <c r="I2035" s="2" t="n">
+        <v>31.1708</v>
+      </c>
+      <c r="J2035" s="2" t="n">
+        <v>31.3773</v>
       </c>
     </row>
     <row r="2036">
-      <c r="A2036" t="inlineStr">
-        <is>
-          <t>TP.DK.USD.A.YTL</t>
-        </is>
-      </c>
-      <c r="B2036" t="inlineStr">
-        <is>
-          <t>(USD)  ABD  Doları  (Döviz  Alış)-Düzey</t>
-        </is>
-      </c>
-      <c r="C2036" t="inlineStr">
-        <is>
-          <t>Gözlem Değeri: Aritmetik Ortalama</t>
-        </is>
-      </c>
-    </row>
+</row>
     <row r="2037">
-      <c r="A2037" t="inlineStr">
-        <is>
-          <t>TP.DK.USD.S.YTL</t>
-        </is>
-      </c>
-      <c r="B2037" t="inlineStr">
-        <is>
-          <t>(USD)  ABD  Doları  (Döviz  Satış)-Düzey</t>
-        </is>
-      </c>
-      <c r="C2037" t="inlineStr">
-        <is>
-          <t>Gözlem Değeri: Aritmetik Ortalama</t>
-        </is>
-      </c>
-    </row>
+</row>
     <row r="2038">
-      <c r="A2038" t="inlineStr">
-        <is>
-          <t>TP.DK.EUR.A.YTL</t>
-        </is>
-      </c>
-      <c r="B2038" t="inlineStr">
-        <is>
-          <t>(EUR)  Euro  (Döviz  Alış)-Düzey</t>
-        </is>
-      </c>
-      <c r="C2038" t="inlineStr">
-        <is>
-          <t>Gözlem Değeri: Aritmetik Ortalama</t>
+      <c r="A2038" s="1" t="inlineStr">
+        <is>
+          <t>Seri Açıklamaları</t>
         </is>
       </c>
     </row>
     <row r="2039">
       <c r="A2039" t="inlineStr">
         <is>
-          <t>TP.DK.EUR.S.YTL</t>
+          <t>TP.BISTTLREF.ORAN</t>
         </is>
       </c>
       <c r="B2039" t="inlineStr">
         <is>
-          <t>(EUR)  Euro  (Döviz  Satış)-Düzey</t>
-        </is>
-      </c>
-      <c r="C2039" t="inlineStr">
-        <is>
-          <t>Gözlem Değeri: Aritmetik Ortalama</t>
+          <t>BIST TLREF -Türk Lirası Gecelik Referans Faiz Oranı (ISIN:TRIXIST00015)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="2040">
       <c r="A2040" t="inlineStr">
         <is>
-          <t>TP.DK.GBP.A.YTL</t>
+          <t>TP.DK.USD.A.YTL</t>
         </is>
       </c>
       <c r="B2040" t="inlineStr">
         <is>
-          <t>(GBP)  İngiliz  Sterlini  (Döviz  Alış)-Düzey</t>
+          <t>(USD)  ABD  Doları  (Döviz  Alış)-Düzey</t>
         </is>
       </c>
       <c r="C2040" t="inlineStr">
@@ -70718,12 +70788,12 @@
     <row r="2041">
       <c r="A2041" t="inlineStr">
         <is>
-          <t>TP.DK.GBP.S.YTL</t>
+          <t>TP.DK.USD.S.YTL</t>
         </is>
       </c>
       <c r="B2041" t="inlineStr">
         <is>
-          <t>(GBP)  İngiliz  Sterlini  (Döviz  Satış)-Düzey</t>
+          <t>(USD)  ABD  Doları  (Döviz  Satış)-Düzey</t>
         </is>
       </c>
       <c r="C2041" t="inlineStr">
@@ -70735,12 +70805,12 @@
     <row r="2042">
       <c r="A2042" t="inlineStr">
         <is>
-          <t>TP.DK.JPY.A.YTL</t>
+          <t>TP.DK.EUR.A.YTL</t>
         </is>
       </c>
       <c r="B2042" t="inlineStr">
         <is>
-          <t>(JPY)  100  Japon  Yeni  (Döviz  Alış)-Düzey</t>
+          <t>(EUR)  Euro  (Döviz  Alış)-Düzey</t>
         </is>
       </c>
       <c r="C2042" t="inlineStr">
@@ -70752,12 +70822,12 @@
     <row r="2043">
       <c r="A2043" t="inlineStr">
         <is>
-          <t>TP.DK.JPY.S.YTL</t>
+          <t>TP.DK.EUR.S.YTL</t>
         </is>
       </c>
       <c r="B2043" t="inlineStr">
         <is>
-          <t>(JPY)  100  Japon  Yeni  (Döviz  Satış)-Düzey</t>
+          <t>(EUR)  Euro  (Döviz  Satış)-Düzey</t>
         </is>
       </c>
       <c r="C2043" t="inlineStr">
@@ -70767,74 +70837,86 @@
       </c>
     </row>
     <row r="2044">
-</row>
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>TP.DK.GBP.A.YTL</t>
+        </is>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>(GBP)  İngiliz  Sterlini  (Döviz  Alış)-Düzey</t>
+        </is>
+      </c>
+      <c r="C2044" t="inlineStr">
+        <is>
+          <t>Gözlem Değeri: Aritmetik Ortalama</t>
+        </is>
+      </c>
+    </row>
     <row r="2045">
-      <c r="A2045" s="1" t="inlineStr">
-        <is>
-          <t>Notlar</t>
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>TP.DK.GBP.S.YTL</t>
+        </is>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>(GBP)  İngiliz  Sterlini  (Döviz  Satış)-Düzey</t>
+        </is>
+      </c>
+      <c r="C2045" t="inlineStr">
+        <is>
+          <t>Gözlem Değeri: Aritmetik Ortalama</t>
         </is>
       </c>
     </row>
     <row r="2046">
       <c r="A2046" t="inlineStr">
         <is>
-          <t>TP.BISTTLREF.ORAN</t>
+          <t>TP.DK.JPY.A.YTL</t>
         </is>
       </c>
       <c r="B2046" t="inlineStr">
         <is>
-          <t>Veri Kaynağı</t>
+          <t>(JPY)  100  Japon  Yeni  (Döviz  Alış)-Düzey</t>
         </is>
       </c>
       <c r="C2046" t="inlineStr">
         <is>
-          <t>BORSA İSTANBUL</t>
+          <t>Gözlem Değeri: Aritmetik Ortalama</t>
         </is>
       </c>
     </row>
     <row r="2047">
-      <c r="A2047"/>
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>TP.DK.JPY.S.YTL</t>
+        </is>
+      </c>
       <c r="B2047" t="inlineStr">
         <is>
-          <t>Metodoloji Linki</t>
+          <t>(JPY)  100  Japon  Yeni  (Döviz  Satış)-Düzey</t>
         </is>
       </c>
       <c r="C2047" t="inlineStr">
         <is>
-          <t>https://www.borsaistanbul.com/veriler/verileralt/tlref-verileri</t>
+          <t>Gözlem Değeri: Aritmetik Ortalama</t>
         </is>
       </c>
     </row>
     <row r="2048">
-      <c r="A2048"/>
-      <c r="B2048" t="inlineStr">
-        <is>
-          <t>Revizyon Politika Linki</t>
-        </is>
-      </c>
-      <c r="C2048" t="inlineStr">
-        <is>
-          <t>https://www.borsaistanbul.com/veriler/verileralt/tlref-verileri</t>
-        </is>
-      </c>
-    </row>
+</row>
     <row r="2049">
-      <c r="A2049"/>
-      <c r="B2049" t="inlineStr">
-        <is>
-          <t>Etiketler</t>
-        </is>
-      </c>
-      <c r="C2049" t="inlineStr">
-        <is>
-          <t>Türk Lirası, Gecelik, Referans, Faiz, Oranı, TLREF</t>
+      <c r="A2049" s="1" t="inlineStr">
+        <is>
+          <t>Notlar</t>
         </is>
       </c>
     </row>
     <row r="2050">
       <c r="A2050" t="inlineStr">
         <is>
-          <t>TP.DK.USD.A.YTL</t>
+          <t>TP.BISTTLREF.ORAN</t>
         </is>
       </c>
       <c r="B2050" t="inlineStr">
@@ -70844,7 +70926,7 @@
       </c>
       <c r="C2050" t="inlineStr">
         <is>
-          <t>TCMB</t>
+          <t>BORSA İSTANBUL</t>
         </is>
       </c>
     </row>
@@ -70852,29 +70934,25 @@
       <c r="A2051"/>
       <c r="B2051" t="inlineStr">
         <is>
-          <t>Etiketler</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C2051" t="inlineStr">
         <is>
-          <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
+          <t>https://www.borsaistanbul.com/veriler/verileralt/tlref-verileri</t>
         </is>
       </c>
     </row>
     <row r="2052">
-      <c r="A2052" t="inlineStr">
-        <is>
-          <t>TP.DK.USD.S.YTL</t>
-        </is>
-      </c>
+      <c r="A2052"/>
       <c r="B2052" t="inlineStr">
         <is>
-          <t>Veri Kaynağı</t>
+          <t>Revizyon Politika Linki</t>
         </is>
       </c>
       <c r="C2052" t="inlineStr">
         <is>
-          <t>TCMB</t>
+          <t>https://www.borsaistanbul.com/veriler/verileralt/tlref-verileri</t>
         </is>
       </c>
     </row>
@@ -70887,14 +70965,14 @@
       </c>
       <c r="C2053" t="inlineStr">
         <is>
-          <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
+          <t>Türk Lirası, Gecelik, Referans, Faiz, Oranı, TLREF</t>
         </is>
       </c>
     </row>
     <row r="2054">
       <c r="A2054" t="inlineStr">
         <is>
-          <t>TP.DK.EUR.A.YTL</t>
+          <t>TP.DK.USD.A.YTL</t>
         </is>
       </c>
       <c r="B2054" t="inlineStr">
@@ -70924,7 +71002,7 @@
     <row r="2056">
       <c r="A2056" t="inlineStr">
         <is>
-          <t>TP.DK.EUR.S.YTL</t>
+          <t>TP.DK.USD.S.YTL</t>
         </is>
       </c>
       <c r="B2056" t="inlineStr">
@@ -70954,7 +71032,7 @@
     <row r="2058">
       <c r="A2058" t="inlineStr">
         <is>
-          <t>TP.DK.GBP.A.YTL</t>
+          <t>TP.DK.EUR.A.YTL</t>
         </is>
       </c>
       <c r="B2058" t="inlineStr">
@@ -70984,7 +71062,7 @@
     <row r="2060">
       <c r="A2060" t="inlineStr">
         <is>
-          <t>TP.DK.GBP.S.YTL</t>
+          <t>TP.DK.EUR.S.YTL</t>
         </is>
       </c>
       <c r="B2060" t="inlineStr">
@@ -71014,7 +71092,7 @@
     <row r="2062">
       <c r="A2062" t="inlineStr">
         <is>
-          <t>TP.DK.JPY.A.YTL</t>
+          <t>TP.DK.GBP.A.YTL</t>
         </is>
       </c>
       <c r="B2062" t="inlineStr">
@@ -71042,45 +71120,49 @@
       </c>
     </row>
     <row r="2064">
-      <c r="A2064"/>
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>TP.DK.GBP.S.YTL</t>
+        </is>
+      </c>
       <c r="B2064" t="inlineStr">
         <is>
-          <t>Notlar</t>
+          <t>Veri Kaynağı</t>
         </is>
       </c>
       <c r="C2064" t="inlineStr">
         <is>
-          <t>100 Japon Yeni= ...TL olarak verilmiştir.</t>
+          <t>TCMB</t>
         </is>
       </c>
     </row>
     <row r="2065">
-      <c r="A2065" t="inlineStr">
-        <is>
-          <t>TP.DK.JPY.S.YTL</t>
-        </is>
-      </c>
+      <c r="A2065"/>
       <c r="B2065" t="inlineStr">
         <is>
+          <t>Etiketler</t>
+        </is>
+      </c>
+      <c r="C2065" t="inlineStr">
+        <is>
+          <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>TP.DK.JPY.A.YTL</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C2065" t="inlineStr">
+      <c r="C2066" t="inlineStr">
         <is>
           <t>TCMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="2066">
-      <c r="A2066"/>
-      <c r="B2066" t="inlineStr">
-        <is>
-          <t>Etiketler</t>
-        </is>
-      </c>
-      <c r="C2066" t="inlineStr">
-        <is>
-          <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
         </is>
       </c>
     </row>
@@ -71088,10 +71170,66 @@
       <c r="A2067"/>
       <c r="B2067" t="inlineStr">
         <is>
+          <t>Etiketler</t>
+        </is>
+      </c>
+      <c r="C2067" t="inlineStr">
+        <is>
+          <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068"/>
+      <c r="B2068" t="inlineStr">
+        <is>
           <t>Notlar</t>
         </is>
       </c>
-      <c r="C2067" t="inlineStr">
+      <c r="C2068" t="inlineStr">
+        <is>
+          <t>100 Japon Yeni= ...TL olarak verilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>TP.DK.JPY.S.YTL</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>Veri Kaynağı</t>
+        </is>
+      </c>
+      <c r="C2069" t="inlineStr">
+        <is>
+          <t>TCMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070"/>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>Etiketler</t>
+        </is>
+      </c>
+      <c r="C2070" t="inlineStr">
+        <is>
+          <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071"/>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>Notlar</t>
+        </is>
+      </c>
+      <c r="C2071" t="inlineStr">
         <is>
           <t>100 Japon Yeni= ...TL olarak verilmiştir.</t>
         </is>
